--- a/out/S01_campus_cafeteria_experience/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/S01_campus_cafeteria_experience/agent3/agent3_test_cases_with_paths.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>9 test(s): TC-FT19, TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24 ...</t>
+          <t>12 test(s): TC-FT19, TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24 ...</t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>20 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
+          <t>23 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE39"/>
+  <dimension ref="A1:AE45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5201,22 +5201,22 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Q6 blocks a blank answer</t>
+          <t>Q6 accepts an answer sitting exactly on its stated maximum</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question.</t>
+          <t>Prove Q6 accepts an answer of exactly 500 characters. A maximum is a limit, so the limit itself is inside the rule. One more than this is already tested as a rejection; an off-by-one in the build sits precisely between the two.</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -5232,12 +5232,12 @@
       <c r="N30" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type nothing, then submit.</t>
+then: At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_BOUNDARY (exactly at the limit)</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type nothing, then submit.</t>
+          <t>At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -5267,23 +5267,22 @@
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y30" s="6" t="inlineStr">
@@ -5314,7 +5313,7 @@
       </c>
       <c r="AD30" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE30" s="6" t="inlineStr">
@@ -5344,12 +5343,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -5359,22 +5358,22 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Q6 quotes the answer given at Q5</t>
+          <t>Q6 accepts punctuation and quotation marks</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q6 accepts an answer containing apostrophes, quotation marks and angle brackets. Its rule constrains length and says nothing about content, so this must be accepted. Quotes and brackets are where survey tools most often break, because nobody wrote the rule down and so nobody tested it.</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -5390,12 +5389,12 @@
       <c r="N31" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_SPECIAL_CHARACTERS</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
@@ -5405,7 +5404,7 @@
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -5435,7 +5434,7 @@
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>1. Q6's wording includes: Yes</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
@@ -5456,7 +5455,7 @@
       </c>
       <c r="AA31" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -5471,7 +5470,7 @@
       </c>
       <c r="AD31" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE31" s="6" t="inlineStr">
@@ -5501,12 +5500,12 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -5516,17 +5515,17 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
+          <t>Q6 refuses an answer of spaces alone</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q6 refuses an answer of spaces alone. The questionnaire marks it compulsory, and spaces are not an answer. This is the commoner real-world failure than a blank, because a respondent pressing the space bar looks like a respondent who answered.</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -5547,12 +5546,12 @@
       <c r="N32" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>WHITESPACE_ONLY</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
@@ -5562,17 +5561,17 @@
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
@@ -5582,23 +5581,23 @@
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. Q6's wording includes: Yes</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X32" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y32" s="6" t="inlineStr">
@@ -5614,12 +5613,12 @@
       </c>
       <c r="AA32" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB32" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
+        </is>
+      </c>
+      <c r="AB32" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC32" s="8" t="inlineStr">
@@ -5629,12 +5628,12 @@
       </c>
       <c r="AD32" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE32" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5643,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -5659,42 +5658,42 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Q7 accepts a normal answer and the survey moves on</t>
+          <t>Q6 blocks a blank answer</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question.</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -5704,59 +5703,59 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
+then: At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>1. Q7 is on screen
-2. the next question shown is Q8</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y33" s="6" t="inlineStr">
@@ -5766,12 +5765,13 @@
       </c>
       <c r="Z33" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
       <c r="AA33" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AD33" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE33" s="6" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>3. Dependency / Piping</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Q7 blocks a blank answer</t>
+          <t>Q6 quotes the answer given at Q5</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
@@ -5861,59 +5861,58 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx
-then: At Q7, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>At Q7, select nothing at all, then submit.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
+          <t>1. Q6's wording includes: Yes</t>
         </is>
       </c>
       <c r="X34" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y34" s="6" t="inlineStr">
@@ -5923,7 +5922,8 @@
       </c>
       <c r="Z34" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
       <c r="AA34" s="6" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AD34" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE34" s="6" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -5973,42 +5973,42 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
+          <t>9. Rule Interaction</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
           <t>1. Flow / Routing</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a normal answer and the survey moves on</t>
+          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -6018,8 +6018,8 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -6064,8 +6064,8 @@
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. Q6 is on screen
+2. Q6's wording includes: Yes</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
@@ -6080,8 +6080,8 @@
       </c>
       <c r="Z35" s="6" t="inlineStr">
         <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
       <c r="AA35" s="6" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AD35" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE35" s="6" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -6146,17 +6146,17 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a valid answer</t>
+          <t>Q7 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -6177,22 +6177,22 @@
       <c r="N36" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “x”, then submit.</t>
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type “x”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -6222,7 +6222,8 @@
       </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q7 is on screen
+2. the next question shown is Q8</t>
         </is>
       </c>
       <c r="X36" s="6" t="inlineStr">
@@ -6237,8 +6238,7 @@
       </c>
       <c r="Z36" s="6" t="inlineStr">
         <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA36" s="6" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="AD36" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE36" s="6" t="inlineStr">
@@ -6273,105 +6273,105 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT31</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Q7 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx
+then: At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U37" s="6" t="inlineStr">
+        <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT31</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>10. Negative / Robustness</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>Q8 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N37" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 501-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="inlineStr">
-        <is>
-          <t>INVALID_BOUNDARY</t>
-        </is>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type a 501-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
-        </is>
-      </c>
-      <c r="S37" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T37" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U37" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
           <t>No forward navigation - the same question must reappear.</t>
@@ -6380,7 +6380,7 @@
       <c r="W37" s="6" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q8</t>
+2. an error message is shown against Q7</t>
         </is>
       </c>
       <c r="X37" s="6" t="inlineStr">
@@ -6395,8 +6395,7 @@
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA37" s="6" t="inlineStr">
@@ -6416,7 +6415,7 @@
       </c>
       <c r="AD37" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE37" s="6" t="inlineStr">
@@ -6446,7 +6445,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -6461,22 +6460,22 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Q8 allows a blank answer, being optional</t>
+          <t>Q8 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -6492,12 +6491,12 @@
       <c r="N38" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type nothing, then submit.</t>
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
@@ -6507,7 +6506,7 @@
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type nothing, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -6537,7 +6536,8 @@
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q8 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X38" s="6" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="AD38" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE38" s="6" t="inlineStr">
@@ -6588,151 +6588,1094 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT33</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Q8 accepts a valid answer</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type “x”, then submit.</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>VALID_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type “x”, then submit.</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T39" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U39" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V39" s="6" t="inlineStr">
+        <is>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
+        </is>
+      </c>
+      <c r="W39" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
+        </is>
+      </c>
+      <c r="X39" s="6" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="Y39" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z39" s="6" t="inlineStr">
+        <is>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
+        </is>
+      </c>
+      <c r="AA39" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB39" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC39" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD39" s="6" t="inlineStr">
+        <is>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+        </is>
+      </c>
+      <c r="AE39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT34</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Q8 rejects an invalid answer</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type a 501-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>INVALID_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type a 501-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T40" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U40" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V40" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W40" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q8</t>
+        </is>
+      </c>
+      <c r="X40" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y40" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z40" s="6" t="inlineStr">
+        <is>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
+        </is>
+      </c>
+      <c r="AA40" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB40" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC40" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD40" s="6" t="inlineStr">
+        <is>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+        </is>
+      </c>
+      <c r="AE40" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT35</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Q8 accepts an answer sitting exactly on its stated maximum</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 accepts an answer of exactly 500 characters. A maximum is a limit, so the limit itself is inside the rule. One more than this is already tested as a rejection; an off-by-one in the build sits precisely between the two.</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type a 500-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>VALID_BOUNDARY (exactly at the limit)</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type a 500-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T41" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U41" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V41" s="6" t="inlineStr">
+        <is>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
+        </is>
+      </c>
+      <c r="W41" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
+        </is>
+      </c>
+      <c r="X41" s="6" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="Y41" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z41" s="6" t="inlineStr">
+        <is>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
+        </is>
+      </c>
+      <c r="AA41" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB41" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC41" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD41" s="6" t="inlineStr">
+        <is>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+        </is>
+      </c>
+      <c r="AE41" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT36</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Q8 accepts punctuation and quotation marks</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 accepts an answer containing apostrophes, quotation marks and angle brackets. Its rule constrains length and says nothing about content, so this must be accepted. Quotes and brackets are where survey tools most often break, because nobody wrote the rule down and so nobody tested it.</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>VALID_SPECIAL_CHARACTERS</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U42" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V42" s="6" t="inlineStr">
+        <is>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
+        </is>
+      </c>
+      <c r="W42" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
+        </is>
+      </c>
+      <c r="X42" s="6" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="Y42" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z42" s="6" t="inlineStr">
+        <is>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
+        </is>
+      </c>
+      <c r="AA42" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB42" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC42" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD42" s="6" t="inlineStr">
+        <is>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+        </is>
+      </c>
+      <c r="AE42" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT37</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Q8 accepts spaces alone, being optional</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 accepts an answer of spaces alone. The questionnaire marks it optional, so nothing about the response may block progress.</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type 3 spaces and nothing else, then submit.</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>WHITESPACE_ONLY</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U43" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V43" s="6" t="inlineStr">
+        <is>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
+        </is>
+      </c>
+      <c r="W43" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
+        </is>
+      </c>
+      <c r="X43" s="6" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="Y43" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z43" s="6" t="inlineStr">
+        <is>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
+        </is>
+      </c>
+      <c r="AA43" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB43" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="AC43" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD43" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE43" s="6" t="inlineStr">
+        <is>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT38</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Q8 allows a blank answer, being optional</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type nothing, then submit.</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type nothing, then submit.</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T44" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U44" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V44" s="6" t="inlineStr">
+        <is>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
+        </is>
+      </c>
+      <c r="W44" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
+        </is>
+      </c>
+      <c r="X44" s="6" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="Y44" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z44" s="6" t="inlineStr">
+        <is>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
+        </is>
+      </c>
+      <c r="AA44" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB44" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC44" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD44" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
           <t>whole survey</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>TC-RT03</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>ROUTE</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>6. Termination / Disposition</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>1. Flow / Routing</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>P03</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J45" s="6" t="inlineStr">
         <is>
           <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
+      <c r="K45" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>Travel path P03 (Completing respondent — Q5=Yes) as far as the end.</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
         <is>
           <t>FRESH_RESPONDENT</t>
         </is>
       </c>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="N45" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O39" s="6" t="inlineStr">
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P39" s="6" t="inlineStr">
+      <c r="P45" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
-      <c r="S39" s="6" t="inlineStr">
+      <c r="S45" s="6" t="inlineStr">
         <is>
           <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
-      <c r="T39" s="6" t="inlineStr">
+      <c r="T45" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U39" s="6" t="inlineStr">
+      <c r="U45" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="V39" s="6" t="inlineStr">
+      <c r="V45" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W39" s="6" t="inlineStr">
+      <c r="W45" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X39" s="6" t="inlineStr">
+      <c r="X45" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y39" s="6" t="inlineStr">
+      <c r="Y45" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z39" s="6" t="inlineStr">
+      <c r="Z45" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA39" s="6" t="inlineStr">
+      <c r="AA45" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB39" s="8" t="inlineStr">
+      <c r="AB45" s="8" t="inlineStr">
         <is>
           <t>RESOLVED</t>
         </is>
       </c>
-      <c r="AC39" s="8" t="inlineStr">
+      <c r="AC45" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD39" s="6" t="inlineStr">
+      <c r="AD45" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE39" s="6" t="inlineStr">
+      <c r="AE45" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
